--- a/Modules/MiniDJ/MiniDJ_BOM.xlsx
+++ b/Modules/MiniDJ/MiniDJ_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\MiniDJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6535CF-93C5-45F8-B521-7860558FE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF5037F-E2BA-4708-8FD0-C0638826ABA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -89,15 +89,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Jack Nut</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
     <t>Alt Link</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <t>240k</t>
   </si>
   <si>
@@ -1620,6 +1611,15 @@
   </si>
   <si>
     <t>*** Use only one standoff. Leave the holes next to the power connector empty.</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
   </si>
 </sst>
 </file>
@@ -2524,7 +2524,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -2547,7 +2547,7 @@
         <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2558,19 +2558,19 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2581,19 +2581,19 @@
         <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2604,19 +2604,19 @@
         <v>220</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -2627,19 +2627,19 @@
         <v>470</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -2650,19 +2650,19 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="J7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -2670,22 +2670,22 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2693,22 +2693,22 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2716,22 +2716,22 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -2742,19 +2742,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="J11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -2762,22 +2762,22 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J12" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -2785,22 +2785,22 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J13" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -2808,22 +2808,22 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J14" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2831,22 +2831,22 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J15" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2854,22 +2854,22 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J16" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2877,22 +2877,22 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J17" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2903,19 +2903,19 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J18" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2923,22 +2923,22 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J19" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2946,22 +2946,22 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J20" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2969,22 +2969,22 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2992,22 +2992,22 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J22" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -3015,22 +3015,22 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J23" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -3038,22 +3038,22 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J24" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -3061,22 +3061,22 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J25" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -3084,22 +3084,22 @@
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J26" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -3107,22 +3107,22 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J27" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -3133,19 +3133,19 @@
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J28" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -3156,19 +3156,19 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J29" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -3176,22 +3176,22 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" t="s">
-        <v>202</v>
-      </c>
-      <c r="E30" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="J30" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -3199,22 +3199,22 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" t="s">
         <v>114</v>
       </c>
-      <c r="C31" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" t="s">
-        <v>117</v>
-      </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J31" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -3222,22 +3222,22 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D32" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E32" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J32" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -3245,22 +3245,22 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D33" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E33" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J33" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -3268,22 +3268,22 @@
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E34" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J34" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -3291,22 +3291,22 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" t="s">
         <v>123</v>
       </c>
-      <c r="C35" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" t="s">
-        <v>125</v>
-      </c>
-      <c r="E35" t="s">
-        <v>126</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J35" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -3314,22 +3314,22 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J36" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -3337,22 +3337,22 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" t="s">
         <v>128</v>
       </c>
-      <c r="D37" t="s">
-        <v>131</v>
-      </c>
       <c r="E37" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J37" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -3360,22 +3360,22 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D38" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J38" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -3383,22 +3383,22 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D39" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E39" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J39" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -3406,22 +3406,22 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E40" t="s">
+        <v>67</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C40" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E40" t="s">
-        <v>70</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="J40" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -3429,22 +3429,22 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J41" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -3452,22 +3452,22 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D42" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J42" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -3475,22 +3475,22 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C43" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J43" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -3498,22 +3498,22 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D44" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E44" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J44" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -3521,22 +3521,22 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E45" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J45" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -3544,13 +3544,13 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E46" t="s">
         <v>12</v>
@@ -3559,7 +3559,7 @@
         <v>15</v>
       </c>
       <c r="J46" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -3567,22 +3567,22 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E47" t="s">
         <v>11</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J47" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -3590,22 +3590,22 @@
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E48" t="s">
         <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J48" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -3613,22 +3613,22 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
+        <v>138</v>
+      </c>
+      <c r="C49" t="s">
         <v>141</v>
       </c>
-      <c r="C49" t="s">
-        <v>144</v>
-      </c>
       <c r="D49" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E49" t="s">
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J49" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -3636,22 +3636,22 @@
         <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C50" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D50" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E50" t="s">
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J50" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -3659,10 +3659,10 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>10</v>
@@ -3671,15 +3671,15 @@
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>41</v>
+        <v>212</v>
       </c>
       <c r="J51" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J52" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -3687,19 +3687,19 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
+        <v>144</v>
+      </c>
+      <c r="C53" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C53" t="s">
-        <v>148</v>
-      </c>
-      <c r="E53" t="s">
-        <v>149</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="J53" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -3707,19 +3707,19 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
+        <v>148</v>
+      </c>
+      <c r="C54" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" t="s">
+        <v>150</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C54" t="s">
-        <v>152</v>
-      </c>
-      <c r="E54" t="s">
-        <v>153</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="J54" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -3727,25 +3727,25 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E55" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J55" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F56" s="2"/>
       <c r="J56" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -3759,13 +3759,13 @@
         <v>17</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="J57" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -3773,19 +3773,19 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
       </c>
       <c r="E58" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>20</v>
+        <v>211</v>
       </c>
       <c r="J58" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -3796,16 +3796,16 @@
         <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E59" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J59" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -3813,19 +3813,19 @@
         <v>3</v>
       </c>
       <c r="B60" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" t="s">
         <v>30</v>
       </c>
-      <c r="C60" t="s">
+      <c r="F60" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E60" t="s">
-        <v>32</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="J60" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -3833,19 +3833,19 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" t="s">
+        <v>158</v>
+      </c>
+      <c r="E61" t="s">
         <v>30</v>
       </c>
-      <c r="C61" t="s">
-        <v>161</v>
-      </c>
-      <c r="E61" t="s">
-        <v>32</v>
-      </c>
       <c r="F61" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J61" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -3853,7 +3853,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -3861,17 +3861,17 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B66" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B67" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -3880,61 +3880,61 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F46" r:id="rId1" xr:uid="{2FFA16CA-1C09-4238-A274-A8E752257B03}"/>
-    <hyperlink ref="F57" r:id="rId2" xr:uid="{7BEFCD36-8AD2-440B-9367-49B26ECC7D44}"/>
-    <hyperlink ref="F58" r:id="rId3" xr:uid="{9DDBFB79-A86F-416F-992C-EA73BF67F62A}"/>
-    <hyperlink ref="F41" r:id="rId4" xr:uid="{A6CF0FA4-29AE-4802-ABF2-732CCD8F5B1A}"/>
-    <hyperlink ref="F60" r:id="rId5" xr:uid="{71BD0A22-CFC6-4535-BC95-485B0B4BDBB1}"/>
-    <hyperlink ref="F59" r:id="rId6" xr:uid="{15373916-8466-4BC6-A723-891CF250D876}"/>
-    <hyperlink ref="F42" r:id="rId7" xr:uid="{61083F9E-CD06-4C67-B2A7-487282B4703F}"/>
-    <hyperlink ref="F4" r:id="rId8" xr:uid="{819C6402-3D5D-4B25-97E0-8692DF28C958}"/>
-    <hyperlink ref="F7" r:id="rId9" xr:uid="{088B380F-0F4E-48C6-B8F4-7C9EA5C9A919}"/>
-    <hyperlink ref="F18" r:id="rId10" xr:uid="{419058FA-6AF9-4657-BB33-870848319318}"/>
-    <hyperlink ref="F21" r:id="rId11" xr:uid="{95403BE5-9965-4775-91A5-703E0DF53AAE}"/>
-    <hyperlink ref="F39" r:id="rId12" xr:uid="{69BAA13E-355F-4E84-88E2-FC7AD0F807EA}"/>
-    <hyperlink ref="F29" r:id="rId13" xr:uid="{D6A14AA2-E6F3-4770-8DF1-AFE04E6C718C}"/>
-    <hyperlink ref="F28" r:id="rId14" xr:uid="{1C9417FF-8036-407C-AB29-8E95DF6D41EE}"/>
-    <hyperlink ref="F30" r:id="rId15" xr:uid="{CC6689E2-C81C-41BE-B0FC-072DD0353CA1}"/>
-    <hyperlink ref="F38" r:id="rId16" xr:uid="{9C3F0609-BA2F-4F77-AA51-1A35D9E691E9}"/>
-    <hyperlink ref="F40" r:id="rId17" xr:uid="{7BE9F748-B11C-43A3-AD9F-561ED820AF56}"/>
-    <hyperlink ref="F45" r:id="rId18" xr:uid="{09701744-5D9A-435D-B0BC-C3C6BEC20EEE}"/>
-    <hyperlink ref="F11" r:id="rId19" xr:uid="{5EBA008A-B955-4E84-A530-B23F31AC47D9}"/>
-    <hyperlink ref="F31" r:id="rId20" xr:uid="{D85BEE54-349C-40DC-90B6-12DD5F579249}"/>
-    <hyperlink ref="F43" r:id="rId21" xr:uid="{9F16E1FA-7C67-4326-9BB8-304FA1510FD1}"/>
-    <hyperlink ref="F53" r:id="rId22" xr:uid="{D5A197EB-F833-40D6-BFB5-E92E722F3CC4}"/>
-    <hyperlink ref="F54" r:id="rId23" xr:uid="{0C89E743-792B-4AC4-B646-5B4F9763F449}"/>
-    <hyperlink ref="F55" r:id="rId24" xr:uid="{40EFFBA0-1B26-4B98-9DE5-8DF0C6469447}"/>
-    <hyperlink ref="F47" r:id="rId25" xr:uid="{D1C34BD4-179A-481E-9F09-70DED7CB2C47}"/>
-    <hyperlink ref="F51" r:id="rId26" xr:uid="{FDBD2295-7CA4-46D8-8CC8-60D13B6EB251}"/>
-    <hyperlink ref="F48" r:id="rId27" xr:uid="{66E14988-7287-4D7D-8F13-CB3BF911C0AE}"/>
-    <hyperlink ref="F50" r:id="rId28" xr:uid="{14CB05AC-0806-451F-980C-40798D2F804B}"/>
-    <hyperlink ref="F49" r:id="rId29" xr:uid="{366622C7-191C-4491-9195-0159A3725CEA}"/>
-    <hyperlink ref="F61" r:id="rId30" xr:uid="{7FE48762-4E22-4649-B27B-341466A71118}"/>
-    <hyperlink ref="F44" r:id="rId31" xr:uid="{CED9A95B-8A9A-435E-92D2-04D334DAC9A6}"/>
-    <hyperlink ref="F3" r:id="rId32" xr:uid="{04F637D1-7181-42E3-9A5B-5CD319A37A25}"/>
-    <hyperlink ref="F5" r:id="rId33" xr:uid="{525D4A0E-FB73-4404-B375-506C0BBF1AB1}"/>
-    <hyperlink ref="F6" r:id="rId34" xr:uid="{99A5F991-A5C3-4E89-AE53-929FD2383098}"/>
-    <hyperlink ref="F9" r:id="rId35" xr:uid="{75129D40-D03C-4D99-A755-9E96A857CF87}"/>
-    <hyperlink ref="F8" r:id="rId36" xr:uid="{27D679D9-BD03-4EA0-B1C4-D99CF5630406}"/>
-    <hyperlink ref="F10" r:id="rId37" xr:uid="{927CFFCC-81DD-4C13-9A42-6E4962069522}"/>
-    <hyperlink ref="F12" r:id="rId38" xr:uid="{90FBDF02-4678-4F2E-A110-7A13B6C236FB}"/>
-    <hyperlink ref="F13" r:id="rId39" xr:uid="{51CA36D2-99DA-4FDB-8722-40360AB26AD7}"/>
-    <hyperlink ref="F14" r:id="rId40" xr:uid="{98C75B2D-0CC3-4043-A1AE-68F73F42D198}"/>
-    <hyperlink ref="F15" r:id="rId41" xr:uid="{10B49596-6C19-46AF-8801-08B472282F35}"/>
-    <hyperlink ref="F16" r:id="rId42" xr:uid="{62BB463D-7B21-4D35-AAA5-A19CF1B24A1E}"/>
-    <hyperlink ref="F17" r:id="rId43" xr:uid="{8CDB7AC6-956E-4697-8EFD-125F3A2FA6C7}"/>
-    <hyperlink ref="F19" r:id="rId44" xr:uid="{7626D5C6-2B15-4A8D-9108-226257108D1A}"/>
-    <hyperlink ref="F20" r:id="rId45" xr:uid="{450BDE85-24BB-4B87-9D9E-C5787FCA7487}"/>
-    <hyperlink ref="F22" r:id="rId46" xr:uid="{C97DE120-C2A6-4746-BD9F-FEF7FE51DD82}"/>
-    <hyperlink ref="F23" r:id="rId47" xr:uid="{FD3D4C81-450E-4098-BE44-67F03800BD30}"/>
-    <hyperlink ref="F24" r:id="rId48" xr:uid="{7C0A4D99-56D7-4C91-98D2-42B7513F39D7}"/>
-    <hyperlink ref="F25" r:id="rId49" xr:uid="{BAE4C2A1-45B1-4425-A1DE-3357B4BEEDFC}"/>
-    <hyperlink ref="F27" r:id="rId50" xr:uid="{44BCA2CD-2191-4A71-8E7B-51968F4F4D8A}"/>
-    <hyperlink ref="F32" r:id="rId51" xr:uid="{FC0E13A6-96C9-4777-B7E4-B436763FE2BB}"/>
-    <hyperlink ref="F33" r:id="rId52" xr:uid="{4935ECCF-C1E9-4407-A17F-09C272C4960B}"/>
-    <hyperlink ref="F34" r:id="rId53" xr:uid="{15FF002E-D140-48D7-86AC-8C1BA16942EE}"/>
-    <hyperlink ref="F35" r:id="rId54" xr:uid="{371DCCBC-06A0-4B07-9E64-4386DFA03FDB}"/>
-    <hyperlink ref="F36" r:id="rId55" xr:uid="{0D4110CB-1F33-4F1B-AE06-389F47059978}"/>
-    <hyperlink ref="F37" r:id="rId56" xr:uid="{C2AC5A57-6D5F-4612-9F0F-D1357E6DF3C6}"/>
+    <hyperlink ref="F41" r:id="rId2" xr:uid="{A6CF0FA4-29AE-4802-ABF2-732CCD8F5B1A}"/>
+    <hyperlink ref="F60" r:id="rId3" xr:uid="{71BD0A22-CFC6-4535-BC95-485B0B4BDBB1}"/>
+    <hyperlink ref="F59" r:id="rId4" xr:uid="{15373916-8466-4BC6-A723-891CF250D876}"/>
+    <hyperlink ref="F42" r:id="rId5" xr:uid="{61083F9E-CD06-4C67-B2A7-487282B4703F}"/>
+    <hyperlink ref="F4" r:id="rId6" xr:uid="{819C6402-3D5D-4B25-97E0-8692DF28C958}"/>
+    <hyperlink ref="F7" r:id="rId7" xr:uid="{088B380F-0F4E-48C6-B8F4-7C9EA5C9A919}"/>
+    <hyperlink ref="F18" r:id="rId8" xr:uid="{419058FA-6AF9-4657-BB33-870848319318}"/>
+    <hyperlink ref="F21" r:id="rId9" xr:uid="{95403BE5-9965-4775-91A5-703E0DF53AAE}"/>
+    <hyperlink ref="F39" r:id="rId10" xr:uid="{69BAA13E-355F-4E84-88E2-FC7AD0F807EA}"/>
+    <hyperlink ref="F29" r:id="rId11" xr:uid="{D6A14AA2-E6F3-4770-8DF1-AFE04E6C718C}"/>
+    <hyperlink ref="F28" r:id="rId12" xr:uid="{1C9417FF-8036-407C-AB29-8E95DF6D41EE}"/>
+    <hyperlink ref="F30" r:id="rId13" xr:uid="{CC6689E2-C81C-41BE-B0FC-072DD0353CA1}"/>
+    <hyperlink ref="F38" r:id="rId14" xr:uid="{9C3F0609-BA2F-4F77-AA51-1A35D9E691E9}"/>
+    <hyperlink ref="F40" r:id="rId15" xr:uid="{7BE9F748-B11C-43A3-AD9F-561ED820AF56}"/>
+    <hyperlink ref="F45" r:id="rId16" xr:uid="{09701744-5D9A-435D-B0BC-C3C6BEC20EEE}"/>
+    <hyperlink ref="F11" r:id="rId17" xr:uid="{5EBA008A-B955-4E84-A530-B23F31AC47D9}"/>
+    <hyperlink ref="F31" r:id="rId18" xr:uid="{D85BEE54-349C-40DC-90B6-12DD5F579249}"/>
+    <hyperlink ref="F43" r:id="rId19" xr:uid="{9F16E1FA-7C67-4326-9BB8-304FA1510FD1}"/>
+    <hyperlink ref="F53" r:id="rId20" xr:uid="{D5A197EB-F833-40D6-BFB5-E92E722F3CC4}"/>
+    <hyperlink ref="F54" r:id="rId21" xr:uid="{0C89E743-792B-4AC4-B646-5B4F9763F449}"/>
+    <hyperlink ref="F55" r:id="rId22" xr:uid="{40EFFBA0-1B26-4B98-9DE5-8DF0C6469447}"/>
+    <hyperlink ref="F47" r:id="rId23" xr:uid="{D1C34BD4-179A-481E-9F09-70DED7CB2C47}"/>
+    <hyperlink ref="F48" r:id="rId24" xr:uid="{66E14988-7287-4D7D-8F13-CB3BF911C0AE}"/>
+    <hyperlink ref="F50" r:id="rId25" xr:uid="{14CB05AC-0806-451F-980C-40798D2F804B}"/>
+    <hyperlink ref="F49" r:id="rId26" xr:uid="{366622C7-191C-4491-9195-0159A3725CEA}"/>
+    <hyperlink ref="F61" r:id="rId27" xr:uid="{7FE48762-4E22-4649-B27B-341466A71118}"/>
+    <hyperlink ref="F44" r:id="rId28" xr:uid="{CED9A95B-8A9A-435E-92D2-04D334DAC9A6}"/>
+    <hyperlink ref="F3" r:id="rId29" xr:uid="{04F637D1-7181-42E3-9A5B-5CD319A37A25}"/>
+    <hyperlink ref="F5" r:id="rId30" xr:uid="{525D4A0E-FB73-4404-B375-506C0BBF1AB1}"/>
+    <hyperlink ref="F6" r:id="rId31" xr:uid="{99A5F991-A5C3-4E89-AE53-929FD2383098}"/>
+    <hyperlink ref="F9" r:id="rId32" xr:uid="{75129D40-D03C-4D99-A755-9E96A857CF87}"/>
+    <hyperlink ref="F8" r:id="rId33" xr:uid="{27D679D9-BD03-4EA0-B1C4-D99CF5630406}"/>
+    <hyperlink ref="F10" r:id="rId34" xr:uid="{927CFFCC-81DD-4C13-9A42-6E4962069522}"/>
+    <hyperlink ref="F12" r:id="rId35" xr:uid="{90FBDF02-4678-4F2E-A110-7A13B6C236FB}"/>
+    <hyperlink ref="F13" r:id="rId36" xr:uid="{51CA36D2-99DA-4FDB-8722-40360AB26AD7}"/>
+    <hyperlink ref="F14" r:id="rId37" xr:uid="{98C75B2D-0CC3-4043-A1AE-68F73F42D198}"/>
+    <hyperlink ref="F15" r:id="rId38" xr:uid="{10B49596-6C19-46AF-8801-08B472282F35}"/>
+    <hyperlink ref="F16" r:id="rId39" xr:uid="{62BB463D-7B21-4D35-AAA5-A19CF1B24A1E}"/>
+    <hyperlink ref="F17" r:id="rId40" xr:uid="{8CDB7AC6-956E-4697-8EFD-125F3A2FA6C7}"/>
+    <hyperlink ref="F19" r:id="rId41" xr:uid="{7626D5C6-2B15-4A8D-9108-226257108D1A}"/>
+    <hyperlink ref="F20" r:id="rId42" xr:uid="{450BDE85-24BB-4B87-9D9E-C5787FCA7487}"/>
+    <hyperlink ref="F22" r:id="rId43" xr:uid="{C97DE120-C2A6-4746-BD9F-FEF7FE51DD82}"/>
+    <hyperlink ref="F23" r:id="rId44" xr:uid="{FD3D4C81-450E-4098-BE44-67F03800BD30}"/>
+    <hyperlink ref="F24" r:id="rId45" xr:uid="{7C0A4D99-56D7-4C91-98D2-42B7513F39D7}"/>
+    <hyperlink ref="F25" r:id="rId46" xr:uid="{BAE4C2A1-45B1-4425-A1DE-3357B4BEEDFC}"/>
+    <hyperlink ref="F27" r:id="rId47" xr:uid="{44BCA2CD-2191-4A71-8E7B-51968F4F4D8A}"/>
+    <hyperlink ref="F32" r:id="rId48" xr:uid="{FC0E13A6-96C9-4777-B7E4-B436763FE2BB}"/>
+    <hyperlink ref="F33" r:id="rId49" xr:uid="{4935ECCF-C1E9-4407-A17F-09C272C4960B}"/>
+    <hyperlink ref="F34" r:id="rId50" xr:uid="{15FF002E-D140-48D7-86AC-8C1BA16942EE}"/>
+    <hyperlink ref="F35" r:id="rId51" xr:uid="{371DCCBC-06A0-4B07-9E64-4386DFA03FDB}"/>
+    <hyperlink ref="F36" r:id="rId52" xr:uid="{0D4110CB-1F33-4F1B-AE06-389F47059978}"/>
+    <hyperlink ref="F37" r:id="rId53" xr:uid="{C2AC5A57-6D5F-4612-9F0F-D1357E6DF3C6}"/>
+    <hyperlink ref="F57" r:id="rId54" xr:uid="{A7B17C53-06C1-4A44-89C9-8D4A8B8FCE0D}"/>
+    <hyperlink ref="F58" r:id="rId55" xr:uid="{C6A3F73A-23D2-4033-9FFB-D7B65F38F2AC}"/>
+    <hyperlink ref="F51" r:id="rId56" xr:uid="{5BA065D6-5EBD-4F53-877E-BA050AD08A2B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
